--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,8 @@
           <t>สำนักงานคณะกรรมการกฤษฎีกา</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0109</t>
-        </is>
+      <c r="C2" t="n">
+        <v>109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -513,10 +511,8 @@
           <t>สำนักงานคณะกรรมการสุขภาพแห่งชาติ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0127</t>
-        </is>
+      <c r="C3" t="n">
+        <v>127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -550,10 +546,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C4" t="n">
+        <v>204</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -587,10 +581,8 @@
           <t>กองทัพเรือ</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0205</t>
-        </is>
+      <c r="C5" t="n">
+        <v>205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -624,10 +616,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C6" t="n">
+        <v>305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -661,10 +651,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C7" t="n">
+        <v>305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -698,10 +686,8 @@
           <t>กรมชลประทาน</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0703</t>
-        </is>
+      <c r="C8" t="n">
+        <v>703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -735,10 +721,8 @@
           <t>กรมประมง</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0705</t>
-        </is>
+      <c r="C9" t="n">
+        <v>705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -772,10 +756,8 @@
           <t>กรมท่าอากาศยาน</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0805</t>
-        </is>
+      <c r="C10" t="n">
+        <v>805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -809,10 +791,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C11" t="n">
+        <v>806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -846,10 +826,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1505</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -883,10 +861,8 @@
           <t>สำนักงานเทคโนโลยีและนวัตกรรมด้านชีววิทยาศาสตร์ (องค์การมหาชน)</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1914</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -920,10 +896,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C14" t="n">
+        <v>2102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -957,10 +931,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C15" t="n">
+        <v>2102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -994,10 +966,8 @@
           <t>สถาบันพระบรมราชชนก</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2117</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1017,6 +987,487 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=324ea5e8-1261-499c-95ad-f573ef48a419</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>กองทัพบก</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0204</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างก่อสร้างงานติดตั้งเครื่องปรับอากาศทดแทน ของ โรงพยาบาลอานันทมหิดล จังหวัดลพบุรี ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bdd8fecb-aa2c-4ef4-bd48-a72d5c221a1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0502</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการค่าใช้จ่ายโครงการค่าจ้างบำรุงรักษาและซ่อมแซมห้องปฏิบัติการระบบเครือข่ายคอมพิวเตอร์ (Data Center) ของสำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2d1c7b53-847a-4bf6-b522-1960eec33718</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>กรมพลศึกษา</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0503</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างจ้างเหมาบริการขนย้ายอุปกรณ์สำนักงานอุปกรณ์ฟิตเนส และเครื่องมือวิทยาศาสตร์การกีฬา ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>★ (อุปกรณ์สำนักงาน)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=68d145d2-7e86-4ce2-83ae-2d369ff13869</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0602</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าลิขสิทธิ์ตามโครงการต่ออายุลิขสิทธิ์การใช้งานเครื่องคอมพิวเตอร์แม่ข่าย และอุปกรณ์เครือข่าย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ad102932-1c37-4684-9245-ad75dc78ac1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0702</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาเอกชนบริการล้างทำความสะอาดและบำรุงรักษาเครื่องปรับอากาศ ภายในอาคารที่ทำการกระทรวงเกษตรและสหกรณ์ ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>★ (เครื่องปรับอากาศ)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=36d7c59c-cec2-4f2d-a850-b67c193ca197</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาชุดกล้องวงจรปิดพร้อมอุปกรณ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>★ (กล้องวงจรปิด)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=08888f93-7ea8-4e78-95a7-c73a160f680b</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>กรมโยธาธิการและผังเมือง</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1507</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์สำนักงาน จำนวน ๖ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์สำนักงาน, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=6ade5ffa-bced-41dd-990a-e25bb0710b03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2c0c619e-e66c-497c-b456-26d731ea5b96</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขอุปกรณ์สนับสนุนห้องปฏิบัติการคอมพิวเตอร์ (Data Center) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d4c700d2-d110-4ee6-944c-fbfe3c3ccda4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลผ่านจอภาพ (Video Conference)  ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>★ (จอภาพ, ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7087adf8-2cc8-4674-a130-694da727ee83</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e684df7d-e4aa-429f-90e2-baf69d050535</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องกระตุกไฟฟ้าหัวใจชนิดอัตโนมัติ พร้อมตู้ตั้งพื้นจอแสดงผล และระบบสัญญาณเตือน จำนวน 10 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>★ (จอแสดงผล)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5fb07982-c16a-4dd2-9379-726a8d5a7710</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>กรมอนามัย</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2109</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบประชุมทางไกลออนไลน์ (Video Conference) ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,10 +1001,8 @@
           <t>กองทัพบก</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0204</t>
-        </is>
+      <c r="C17" t="n">
+        <v>204</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1038,10 +1036,8 @@
           <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0502</t>
-        </is>
+      <c r="C18" t="n">
+        <v>502</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1075,10 +1071,8 @@
           <t>กรมพลศึกษา</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0503</t>
-        </is>
+      <c r="C19" t="n">
+        <v>503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1112,10 +1106,8 @@
           <t>สำนักงานปลัดกระทรวงการพัฒนาสังคมและความมั่นคงของมนุษย์</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0602</t>
-        </is>
+      <c r="C20" t="n">
+        <v>602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1149,10 +1141,8 @@
           <t>สำนักงานปลัดกระทรวงเกษตรและสหกรณ์</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0702</t>
-        </is>
+      <c r="C21" t="n">
+        <v>702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1186,10 +1176,8 @@
           <t>กรมป้องกันและบรรเทาสาธารณภัย</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1506</t>
-        </is>
+      <c r="C22" t="n">
+        <v>1506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1223,10 +1211,8 @@
           <t>กรมโยธาธิการและผังเมือง</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1507</t>
-        </is>
+      <c r="C23" t="n">
+        <v>1507</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1260,10 +1246,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C24" t="n">
+        <v>1611</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1297,10 +1281,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C25" t="n">
+        <v>1611</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1334,10 +1316,8 @@
           <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1611</t>
-        </is>
+      <c r="C26" t="n">
+        <v>1611</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1371,10 +1351,8 @@
           <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="C27" t="n">
+        <v>1704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1408,10 +1386,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1445,10 +1421,8 @@
           <t>กรมอนามัย</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2109</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2109</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1468,6 +1442,561 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e9299467-894b-4d9f-930b-0673992d5759</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=d69cee18-1259-45c6-a63e-c0d7537f5335</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0502</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการจ้างบริการบำรุงรักษาและซ่อมแซมแก้ไขคอมพิวเตอร์ลูกข่ายและระบบเครือข่ายคอมพิวเตอร์ พร้อมทั้งอุปกรณ์ต่อพ่วง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=5925e432-6a1c-4246-aab2-f2094aeabd5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อวัสดุคอมพิวเตอร์ จำนวน 2 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=69b5d49d-35a2-49b6-9c69-a77a74df0e9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>กรมทางหลวง</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0806</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์งานบ้านงานครัว จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4b934857-93a6-4ef0-9708-1c258599416f</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางราง</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0812</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์คอมพิวเตอร์และอุปกรณ์ต่อพ่วง พร้อมการติดตั้ง จำนวน ๔ รายการ ของกรมการขนส่งทางราง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f5fcf75f-2a16-470f-9a41-1d640b04b1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0911</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างต่ออายุสมาชิกโปรแกรมและบำรุงรักษาซ่อมแซมแก้ไขคอมพิวเตอร์แม่ข่ายและอุปกรณ์เครือข่ายไร้สาย ปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, อุปกรณ์เครือข่าย)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=c3327ec9-d212-4e24-aafb-36bbf05f5a34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าคอมพิวเตอร์และอุปกรณ์ที่เกี่ยวข้อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1fb72e55-1c99-4e44-b4b3-370e1c2e8711</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าระบบประชุมทางไกล (Web Conference Video Streaming) ของสำนักงานปลัดกระทรวงพาณิชย์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>★ (ระบบประชุมทางไกล)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3d156308-f0d2-4d07-bf4a-27913c2c22b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อโต๊ะและเก้าอี้เพื่อใช้ในราชการของสำนักงานที่ดินจังหวัดพิษณุโลก และสาขาฯ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>★ (โต๊ะ, เก้าอี้)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=341e9241-c067-4ffa-9e06-734f19c6b999</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>กรมพัฒนาฝีมือแรงงาน</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาครุภัณฑ์คอมพิวเตอร์และระบบเครือข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=677d75a8-aa89-4b8b-a742-eca4be741031</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ จำนวน ๓ รายการ ของสำนักงานสาธารณสุขจังหวัดกาญจนบุรี เพื่อโรงพยาบาลชุมชน จำนวน ๑๐ แห่ง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=0424125a-176e-423d-9959-61c0ef9229f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องติดตามการทำงานของหัวใจและสัญญาณชีพ 6 พารามิเตอร์ ระบบรวมศูนย์ไม่น้อยกว่า 4 เตียง จำนวน 1 เครื่อง งบประมาณกองสลากการกุศล ในโครงการสนับสนุนครุภัณฑ์การแพทย์เพื่อเพิ่มศักยภาพโรงพยาบาลในพื้นที่ที่ได้รับผลกระทบจากสถานการณ์สู้รบชายแดนไทย - กัมพูชา ปีงบประมาณ พ.ศ.2569 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ee066bf2-4c21-4580-8391-e1257afc7b11</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อตู้เย็นเก็บเลือดขนาดไม่น้อยกว่า 20 คิว จำนวน 1 เครื่อง สำหรับ รพ.พระปิยมหาราช ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>★ (ตู้เย็น)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=985c4332-e608-4dc3-883b-e90257b97ad3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 13 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=db849b83-870c-446d-a004-6e2462b1b3a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
         </is>
       </c>
     </row>

--- a/Backup/eGP_Monthly_Main_202609.xlsx
+++ b/Backup/eGP_Monthly_Main_202609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1456,10 +1456,8 @@
           <t>กรมศุลกากร</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0305</t>
-        </is>
+      <c r="C30" t="n">
+        <v>305</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1493,10 +1491,8 @@
           <t>สำนักงานปลัดกระทรวงการท่องเที่ยวและกีฬา</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0502</t>
-        </is>
+      <c r="C31" t="n">
+        <v>502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1530,10 +1526,8 @@
           <t>กรมการขนส่งทางบก</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0804</t>
-        </is>
+      <c r="C32" t="n">
+        <v>804</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1567,10 +1561,8 @@
           <t>กรมทางหลวง</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0806</t>
-        </is>
+      <c r="C33" t="n">
+        <v>806</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1604,10 +1596,8 @@
           <t>กรมการขนส่งทางราง</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0812</t>
-        </is>
+      <c r="C34" t="n">
+        <v>812</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1641,10 +1631,8 @@
           <t>สำนักงานนโยบายและแผนทรัพยากรธรรมชาติและสิ่งแวดล้อม</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0911</t>
-        </is>
+      <c r="C35" t="n">
+        <v>911</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1678,10 +1666,8 @@
           <t>สำนักงานกองทุนน้ำมันเชื้อเพลิง</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
+      <c r="C36" t="n">
+        <v>1207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1715,10 +1701,8 @@
           <t>สำนักงานปลัดกระทรวงพาณิชย์</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
+      <c r="C37" t="n">
+        <v>1302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1752,10 +1736,8 @@
           <t>กรมที่ดิน</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
+      <c r="C38" t="n">
+        <v>1505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1789,10 +1771,8 @@
           <t>กรมพัฒนาฝีมือแรงงาน</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="C39" t="n">
+        <v>1704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1826,10 +1806,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C40" t="n">
+        <v>2102</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1863,10 +1841,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C41" t="n">
+        <v>2102</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1900,10 +1876,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C42" t="n">
+        <v>2102</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1937,10 +1911,8 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="C43" t="n">
+        <v>2102</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1974,29 +1946,767 @@
           <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="n">
+        <v>2102</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการคลัง</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0302</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อโครงการจัดซื้อสิทธิ์การใช้งานซอฟต์แวร์ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=1732e367-2c09-431f-abc1-7384c0a94e8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>กรมศุลกากร</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0305</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ประกวดราคาเช่าโครงการจัดเช่าวงจรเครือข่ายสื่อสารเพื่อการเชื่อมโยงข้อมูลระหว่างศูนย์คอมพิวเตอร์ (DC-DR) กรมศุลกากร ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a09e3df4-34c1-4388-a91a-31d0494ea9da</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงการต่างประเทศ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการทำความสะอาด ณ อาคารกระทรวงการต่างประเทศ ถนนศรีอยุธยา อาคารกรมการกงสุลรวมถึงกองบรรณสารและห้องสมุด (ฝ่ายบรรณสาร) และศูนย์ราชการเฉลิมพระเกียรติฯ อาคาร B ชั้น 7 - 8 รวม 3 แห่ง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>★ (สมุด)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=61256c96-a851-4486-ba34-aeb06311fa64</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>กรมชลประทาน</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0703</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องสูบน้ำชนิดหอยโข่ง เเบบ End Suction ขับด้วยมอเตอร์ไฟฟ้า พร้อมติดตั้งอุปกรณ์ เเละระบบควบคุมไฟฟ้า ตามรายละเอียดคุณลักษณะเฉพาะ (Specification) ของกรมชลประทาน และอื่นๆ รวม ๓ รายการ สำหรับงานสถานีสูบน้ำด้วยไฟฟ้าพร้อมระบบส่งน้ำฝายคลองพอถาก ตำบลหน้าเขา อำเภอเขาพนม จังหวัดกระบี่ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>★ (มอเตอร์)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=f690008d-6ff3-4f11-84a7-08da3de166d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมแก้ไขระบบคอมพิวเตอร์ Server และอุปกรณ์ที่ติดตั้ง ณ อาคารระบบข้อมูลกลางและสำรองข้อมูล สำนักงานขนส่งจังหวัดนนทบุรี ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=7dbc77ce-d778-424c-9618-b2cc1659f8ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>กรมการขนส่งทางบก</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0804</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบำรุงรักษาและซ่อมแซมระบบคอมพิวเตอร์แม่ข่ายเสมือน (Server Virtualization) สำหรับให้บริการหน่วยงานต่างๆ ของกรมการขนส่งทางบกที่ใช้ในการสนับสนุน การปฏิบัติงานด้านความปลอดภัย ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=60f2364f-32ae-4a8c-8c92-9936327bd8f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>กรมทรัพยากรทางทะเลและชายฝั่ง</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างโครงการเช่าใช้บริการอินเทอร์เน็ตและสายสัญญาณเครือข่ายพร้อมอุปกรณ์ กรมทรัพยากรทางทะเลและชายฝั่ง ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>★ (สายสัญญาณ)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ab266c44-4e3d-4e4c-a44e-a5e06ffb7d51</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>กรมที่ดิน</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1505</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และระบบคอมพิวเตอร์แม่ข่าย ประจำปีงบประมาณ พ.ศ. ๒๕๗๐ ระยะเวลา ๑๒ เดือน  ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ba59f24a-325d-4e38-8d86-eadcece33632</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างเหมาบริการถ่ายเอกสารพร้อมเครื่องถ่ายเอกสาร กระดาษ วัสดุสิ้นเปลือง และพนักงานประจำเครื่องของสำนักงาน ป.ป.ส. ดินแดง สำนักงาน ปปส.ทุ่งสองห้อง ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>★ (กระดาษ)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=ef490410-ac68-4d7a-9e38-c4dbf7dd4191</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาซอฟต์แวร์และอุปกรณ์ระบบรักษาความปลอดภัยระบบเครือข่ายศูนย์คอมพิวเตอร์สำรอง ( DR-Site Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a430ff3c-1d84-458b-8d71-d54f8c065644</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาระบบป้องกันการบุกรุกเครือข่ายคอมพิวเตอร์ สำนักงาน ป.ป.ส. (Client Zone Firewall) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=bfcbc7fd-4a5c-46e3-b5eb-5b51397db1cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและซ่อมแซมแก้ไขอุปกรณ์เครื่องคอมพิวเตอร์แม่ข่ายพร้อมระบบปฏิบัติการ (Server) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ระบบปฏิบัติการ)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=4a59a370-30a9-4f35-abcd-cec87b36ed1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาอุปกรณ์และซอฟต์แวร์ป้องกันระบบเครือข่าย (Firewall/Virus/VPN) ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>★ (ซอฟต์แวร์)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=71058768-3f32-47a5-b07d-d89703297e8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>สำนักงานคณะกรรมการป้องกันและปราบปรามยาเสพติด</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ประกวดราคาจ้างบำรุงรักษาและแก้ไขปัญหาการใช้เครื่องคอมพิวเตอร์ลูกข่ายและอุปกรณ์ต่อพ่วง สำนักงาน ป.ป.ส. ประจำปีงบประมาณ พ.ศ. 2570 ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=04f4a224-3c0a-4630-9981-263ded303a56</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>กรมส่งเสริมการเรียนรู้</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์คอมพิวเตอร์ จำนวน ๗ รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>★ (คอมพิวเตอร์, ครุภัณฑ์คอมพิวเตอร์, ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=114943ef-9465-4b1b-af6c-d1fbd3564e05</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
         <is>
           <t>2102</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องกระตุกไฟฟ้าหัวใจชนิดไบเฟสิค พร้อมภาควัดออกซิเจนในเลือดของโรงพยาบาลในจังหวัดสุรินทร์ 4 แห่ง จำนวน 5 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>ไม่ระบุ</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการเครื่องดมยาสลบชนิดมาตรฐาน  จำนวน  ๑  เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>★ (ครุภัณฑ์)</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e2347540-427f-4618-ac0a-6d2933980a00</t>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=e1f11ae5-c3d5-4fdc-a76f-351add1653a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์รายการกล้องส่องตรวจและผ่าตัดภายในช่องท้องชนิดวีดิทัศน์แบบคมชัดสูงชนิดภาพ ๒ มิติ จำนวน ๑ เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=3ff66642-757c-4554-a147-37146918afe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อจัดซื้อครุภัณฑ์โครงการจัดซื้อครุภัณฑ์การแพทย์เพื่อการบริการประชาชน จำนวน 4 รายการ ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=921cfd0c-6740-4e24-84ce-20ad0ebfb382</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>สำนักงานปลัดกระทรวงสาธารณสุข</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อครุภัณฑ์การแพทย์ รายการเครื่องช่วยหายใจชนิดควบคุมด้วยปริมาตรและความดันเคลื่อนย้ายได้ ของโรงพยาบาลชุมชน 8 แห่ง จำนวน 11 เครื่อง ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>★ (ครุภัณฑ์)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=2ac905f2-26be-4df4-b481-22676581f31a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>สำนักงานหลักประกันสุขภาพแห่งชาติ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ประกวดราคาซื้อเครื่องฟอกอากาศ แขวงทุ่งสองห้อง เขตหลักสี่ กรุงเทพมหานคร ด้วยวิธีประกวดราคาอิเล็กทรอนิกส์ (e-bidding)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ไม่ระบุ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>★ (เครื่องฟอกอากาศ)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://process5.gprocurement.go.th/egp-template-service/dwnt/view-pdf-file?templateId=a91dc5dd-5f0e-49d2-8b3f-d7da9560b550</t>
         </is>
       </c>
     </row>
